--- a/hddt-SES/src/main/resources/static/agent/MauUpload_PXK_HKGDL_TT78.xlsx
+++ b/hddt-SES/src/main/resources/static/agent/MauUpload_PXK_HKGDL_TT78.xlsx
@@ -1,40 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VAN HAU\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1B236B-E5A4-41D3-ABDD-8E01EFD69CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>ASIA</author>
   </authors>
   <commentList>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{34540195-D53E-4136-990C-0BB539C8BDF3}">
+    <comment ref="X1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="13"/>
-            <color indexed="81"/>
             <rFont val="Times New Roman"/>
-            <family val="1"/>
+            <charset val="134"/>
           </rPr>
           <t>Tính chất hàng hóa, dịch vụ
 1: HH/DV
@@ -49,7 +55,55 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
+  <si>
+    <t>Số phiếu(*)</t>
+  </si>
+  <si>
+    <t>Ngày xuất(*)</t>
+  </si>
+  <si>
+    <t>Người điều động(*)</t>
+  </si>
+  <si>
+    <t>Về việc(*)</t>
+  </si>
+  <si>
+    <t>Hợp đồng kinh tế số(*)</t>
+  </si>
+  <si>
+    <t>Hợp đồng kinh tế ngày(*)</t>
+  </si>
+  <si>
+    <t>Người vận chuyển(*)</t>
+  </si>
+  <si>
+    <t>Phương tiện vận chuyển(*)</t>
+  </si>
+  <si>
+    <t>Xuất tại kho - Mã kho(*)</t>
+  </si>
+  <si>
+    <t>Nhập tại kho - Mã kho(*)</t>
+  </si>
+  <si>
+    <t>MST người xuất</t>
+  </si>
+  <si>
+    <t>Họ và tên người xuất</t>
+  </si>
+  <si>
+    <t>Tên đơn vị</t>
+  </si>
+  <si>
+    <t>Email nhận</t>
+  </si>
+  <si>
+    <t>STT(*)</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm(*)</t>
+  </si>
   <si>
     <t>Mã sản phẩm</t>
   </si>
@@ -57,118 +111,88 @@
     <t>Đơn vị tính</t>
   </si>
   <si>
+    <t>Thực xuất(*)</t>
+  </si>
+  <si>
     <t>Thực nhập</t>
   </si>
   <si>
+    <t>Đơn giá(*)</t>
+  </si>
+  <si>
+    <t>Thành tiền(*)</t>
+  </si>
+  <si>
+    <t>Tổng tiền(*)</t>
+  </si>
+  <si>
+    <t>Tính Chất(*)</t>
+  </si>
+  <si>
+    <t>Số tiền bằng chữ</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>03/03/2023</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn A</t>
+  </si>
+  <si>
     <t>Chuyển kho</t>
   </si>
   <si>
+    <t>KT01</t>
+  </si>
+  <si>
     <t>Nguyen Van C</t>
   </si>
   <si>
     <t>Xe tải</t>
   </si>
   <si>
+    <t>WH01</t>
+  </si>
+  <si>
+    <t>WH02</t>
+  </si>
+  <si>
+    <t>sản phẩm 1</t>
+  </si>
+  <si>
     <t>SP001</t>
   </si>
   <si>
     <t>CAI</t>
   </si>
   <si>
-    <t>Email nhận</t>
-  </si>
-  <si>
-    <t>Số tiền bằng chữ</t>
-  </si>
-  <si>
-    <t>WH01</t>
-  </si>
-  <si>
-    <t>WH02</t>
-  </si>
-  <si>
-    <t>sản phẩm 1</t>
+    <t>2</t>
   </si>
   <si>
     <t>sản phẩm 2</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>Nguyễn Văn B</t>
+  </si>
+  <si>
+    <t>KT02</t>
   </si>
   <si>
     <t>Nguyen Van D</t>
   </si>
   <si>
+    <t>xxx@gmail.com</t>
+  </si>
+  <si>
     <t>sp1</t>
   </si>
   <si>
     <t>gói</t>
   </si>
   <si>
-    <t>Số phiếu(*)</t>
-  </si>
-  <si>
-    <t>Ngày xuất(*)</t>
-  </si>
-  <si>
-    <t>Về việc(*)</t>
-  </si>
-  <si>
-    <t>Người vận chuyển(*)</t>
-  </si>
-  <si>
-    <t>Phương tiện vận chuyển(*)</t>
-  </si>
-  <si>
-    <t>Xuất tại kho - Mã kho(*)</t>
-  </si>
-  <si>
-    <t>Nhập tại kho - Mã kho(*)</t>
-  </si>
-  <si>
-    <t>STT(*)</t>
-  </si>
-  <si>
-    <t>Tên sản phẩm(*)</t>
-  </si>
-  <si>
-    <t>Thực xuất(*)</t>
-  </si>
-  <si>
-    <t>Tổng tiền(*)</t>
-  </si>
-  <si>
-    <t>Thành tiền(*)</t>
-  </si>
-  <si>
-    <t>Đơn giá(*)</t>
-  </si>
-  <si>
-    <t>Người điều động(*)</t>
-  </si>
-  <si>
-    <t>Tính Chất(*)</t>
-  </si>
-  <si>
-    <t>xxx@gmail.com</t>
-  </si>
-  <si>
-    <t>Hợp đồng kinh tế số(*)</t>
-  </si>
-  <si>
-    <t>Hợp đồng kinh tế ngày(*)</t>
-  </si>
-  <si>
-    <t>MST người xuất</t>
-  </si>
-  <si>
-    <t>Họ và tên người xuất</t>
-  </si>
-  <si>
-    <t>Tên đơn vị</t>
+    <t>END</t>
   </si>
   <si>
     <t>Hình thức thanh toán</t>
@@ -202,84 +226,217 @@
   </si>
   <si>
     <t>5: Không thu tiền</t>
-  </si>
-  <si>
-    <t>KT01</t>
-  </si>
-  <si>
-    <t>KT02</t>
-  </si>
-  <si>
-    <t>03/03/2023</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn A</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
-      <color indexed="81"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -288,24 +445,210 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -315,64 +658,346 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -421,7 +1046,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -454,26 +1079,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -506,23 +1114,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -693,325 +1284,332 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y4"/>
-  <sheetFormatPr defaultColWidth="25.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Y5"/>
+  <sheetFormatPr defaultColWidth="25.4571428571429" defaultRowHeight="16.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="5" width="25.453125" style="5"/>
-    <col min="6" max="6" width="26.453125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="25.453125" style="5"/>
-    <col min="8" max="8" width="30.81640625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="29.453125" style="5" customWidth="1"/>
-    <col min="10" max="13" width="29.1796875" style="5" customWidth="1"/>
-    <col min="14" max="18" width="25.453125" style="5"/>
-    <col min="19" max="23" width="25.453125" style="6"/>
-    <col min="24" max="24" width="25.453125" style="8"/>
-    <col min="25" max="25" width="25.453125" style="6"/>
-    <col min="26" max="16384" width="25.453125" style="7"/>
+    <col min="1" max="5" width="25.4571428571429" style="3"/>
+    <col min="6" max="6" width="26.4571428571429" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.4571428571429" style="3"/>
+    <col min="8" max="8" width="30.8190476190476" style="3" customWidth="1"/>
+    <col min="9" max="9" width="29.4571428571429" style="3" customWidth="1"/>
+    <col min="10" max="13" width="29.1809523809524" style="3" customWidth="1"/>
+    <col min="14" max="18" width="25.4571428571429" style="3"/>
+    <col min="19" max="23" width="25.4571428571429" style="4"/>
+    <col min="24" max="24" width="25.4571428571429" style="5"/>
+    <col min="25" max="25" width="25.4571428571429" style="4"/>
+    <col min="26" max="16384" width="25.4571428571429" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="2" customFormat="1" spans="1:25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="V1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="J2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="R2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S2" s="4">
+        <v>1</v>
+      </c>
+      <c r="U2" s="4">
         <v>0</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="U1" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="V1" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="W1" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="X1" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="S2" s="6">
-        <v>1</v>
-      </c>
-      <c r="U2" s="6">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6">
+      <c r="V2" s="4">
         <f t="shared" ref="V2:V3" si="0">S2*U2</f>
         <v>0</v>
       </c>
-      <c r="W2" s="6">
+      <c r="W2" s="4">
         <v>0</v>
       </c>
-      <c r="X2" s="8">
+      <c r="X2" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="O3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="S3" s="6">
+    <row r="3" spans="1:24">
+      <c r="A3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="4">
         <v>2</v>
       </c>
-      <c r="U3" s="6">
+      <c r="U3" s="4">
         <v>0</v>
       </c>
-      <c r="V3" s="6">
+      <c r="V3" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W3" s="6">
+      <c r="W3" s="4">
         <v>0</v>
       </c>
-      <c r="X3" s="8">
+      <c r="X3" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="S4" s="6">
+    <row r="4" spans="1:24">
+      <c r="A4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" s="4">
         <v>12</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="4">
         <v>0</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="4">
         <v>0</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="4">
         <v>0</v>
       </c>
-      <c r="X4" s="8">
+      <c r="X4" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N4" r:id="rId1" xr:uid="{74CCD1CE-58A0-4937-B993-958DA0F56A81}"/>
+    <hyperlink ref="N4" r:id="rId3" display="xxx@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="24.5428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>41</v>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/hddt-SES/src/main/resources/static/agent/MauUpload_PXK_HKGDL_TT78.xlsx
+++ b/hddt-SES/src/main/resources/static/agent/MauUpload_PXK_HKGDL_TT78.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -33,7 +33,24 @@
     <author>ASIA</author>
   </authors>
   <commentList>
-    <comment ref="X1" authorId="0">
+    <comment ref="Z1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="13"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Tính chất hàng hóa, dịch vụ
+1: HH/DV
+2: KM
+3: GK
+4: Ghi chú</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,48 +72,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
-  <si>
-    <t>Số phiếu(*)</t>
-  </si>
-  <si>
-    <t>Ngày xuất(*)</t>
-  </si>
-  <si>
-    <t>Người điều động(*)</t>
-  </si>
-  <si>
-    <t>Về việc(*)</t>
-  </si>
-  <si>
-    <t>Hợp đồng kinh tế số(*)</t>
-  </si>
-  <si>
-    <t>Hợp đồng kinh tế ngày(*)</t>
-  </si>
-  <si>
-    <t>Người vận chuyển(*)</t>
-  </si>
-  <si>
-    <t>Phương tiện vận chuyển(*)</t>
-  </si>
-  <si>
-    <t>Xuất tại kho - Mã kho(*)</t>
-  </si>
-  <si>
-    <t>Nhập tại kho - Mã kho(*)</t>
-  </si>
-  <si>
-    <t>MST người xuất</t>
-  </si>
-  <si>
-    <t>Họ và tên người xuất</t>
-  </si>
-  <si>
-    <t>Tên đơn vị</t>
-  </si>
-  <si>
-    <t>Email nhận</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="63">
+  <si>
+    <t>Mã phiếu(*)</t>
+  </si>
+  <si>
+    <t>Địa chỉ xuất kho (*)</t>
+  </si>
+  <si>
+    <t>Ngày lập (*)</t>
+  </si>
+  <si>
+    <t>Họ và tên người xuất kho (*)</t>
+  </si>
+  <si>
+    <t>Loại tiền (*)</t>
+  </si>
+  <si>
+    <t>Tên người vận chuyển (*)</t>
+  </si>
+  <si>
+    <t>Hợp đồng kinh tế số (*)</t>
+  </si>
+  <si>
+    <t>Hợp đồng kinh tế ngày (*)</t>
+  </si>
+  <si>
+    <t>Phương tiện vận chuyển (*)</t>
+  </si>
+  <si>
+    <t>Mã số thuế người nhập</t>
+  </si>
+  <si>
+    <t>Họ và Tên người nhập</t>
+  </si>
+  <si>
+    <t>Tên đơn vị nhập</t>
+  </si>
+  <si>
+    <t>Địa chỉ nhập kho (*)</t>
+  </si>
+  <si>
+    <t>Nội dung nhập kho</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t>Số tài khoản</t>
+  </si>
+  <si>
+    <t>Tại ngân hàng</t>
   </si>
   <si>
     <t>STT(*)</t>
@@ -111,10 +140,7 @@
     <t>Đơn vị tính</t>
   </si>
   <si>
-    <t>Thực xuất(*)</t>
-  </si>
-  <si>
-    <t>Thực nhập</t>
+    <t>Số lượng(*)</t>
   </si>
   <si>
     <t>Đơn giá(*)</t>
@@ -123,40 +149,40 @@
     <t>Thành tiền(*)</t>
   </si>
   <si>
-    <t>Tổng tiền(*)</t>
-  </si>
-  <si>
     <t>Tính Chất(*)</t>
   </si>
   <si>
-    <t>Số tiền bằng chữ</t>
+    <t>Tỷ giá(*)</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>03/03/2023</t>
+    <t>Địa chỉ xuất kho 1</t>
+  </si>
+  <si>
+    <t>12/05/2026</t>
   </si>
   <si>
     <t>Nguyễn Văn A</t>
   </si>
   <si>
-    <t>Chuyển kho</t>
-  </si>
-  <si>
-    <t>KT01</t>
-  </si>
-  <si>
-    <t>Nguyen Van C</t>
-  </si>
-  <si>
-    <t>Xe tải</t>
-  </si>
-  <si>
-    <t>WH01</t>
-  </si>
-  <si>
-    <t>WH02</t>
+    <t>VND</t>
+  </si>
+  <si>
+    <t>Trần Văn A</t>
+  </si>
+  <si>
+    <t>01002/HĐKG/2026</t>
+  </si>
+  <si>
+    <t>Xe</t>
+  </si>
+  <si>
+    <t>Tên đơn vị nhạp 1</t>
+  </si>
+  <si>
+    <t>Địa chỉ kho nhập 1</t>
   </si>
   <si>
     <t>sản phẩm 1</t>
@@ -168,28 +194,37 @@
     <t>CAI</t>
   </si>
   <si>
+    <t>200000</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>sản phẩm 2</t>
   </si>
   <si>
-    <t>Nguyễn Văn B</t>
-  </si>
-  <si>
-    <t>KT02</t>
-  </si>
-  <si>
-    <t>Nguyen Van D</t>
-  </si>
-  <si>
-    <t>xxx@gmail.com</t>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>Trần Văn B</t>
+  </si>
+  <si>
+    <t>Tàu</t>
+  </si>
+  <si>
+    <t>Tên đơn vị nhạp 2</t>
+  </si>
+  <si>
+    <t>Địa chỉ kho nhập 2</t>
   </si>
   <si>
     <t>sp1</t>
   </si>
   <si>
     <t>gói</t>
+  </si>
+  <si>
+    <t>50000</t>
   </si>
   <si>
     <t>END</t>
@@ -287,8 +322,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -436,7 +472,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,7 +487,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,12 +662,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,26 +802,26 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -905,42 +935,56 @@
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -950,12 +994,12 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1290,263 +1334,283 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultColWidth="25.4571428571429" defaultRowHeight="16.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="5" width="25.4571428571429" style="3"/>
-    <col min="6" max="6" width="26.4571428571429" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.4571428571429" style="3"/>
-    <col min="8" max="8" width="30.8190476190476" style="3" customWidth="1"/>
-    <col min="9" max="9" width="29.4571428571429" style="3" customWidth="1"/>
-    <col min="10" max="13" width="29.1809523809524" style="3" customWidth="1"/>
-    <col min="14" max="18" width="25.4571428571429" style="3"/>
-    <col min="19" max="23" width="25.4571428571429" style="4"/>
-    <col min="24" max="24" width="25.4571428571429" style="5"/>
-    <col min="25" max="25" width="25.4571428571429" style="4"/>
-    <col min="26" max="16384" width="25.4571428571429" style="6"/>
+    <col min="1" max="2" width="25.4571428571429" style="3"/>
+    <col min="3" max="3" width="25.4571428571429" style="4"/>
+    <col min="4" max="4" width="33.7142857142857" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.4571428571429" style="4"/>
+    <col min="6" max="6" width="29.8571428571429" style="3" customWidth="1"/>
+    <col min="7" max="7" width="28" style="3" customWidth="1"/>
+    <col min="8" max="8" width="30.8571428571429" style="4" customWidth="1"/>
+    <col min="9" max="9" width="32.4285714285714" style="3" customWidth="1"/>
+    <col min="10" max="10" width="27.1428571428571" style="3" customWidth="1"/>
+    <col min="11" max="22" width="25.4571428571429" style="3"/>
+    <col min="23" max="26" width="25.4571428571429" style="5"/>
+    <col min="27" max="27" width="25.4571428571429" style="6"/>
+    <col min="28" max="16384" width="25.4571428571429" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:25">
-      <c r="A1" s="7" t="s">
+    <row r="1" s="2" customFormat="1" spans="1:27">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="T1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Y1" s="13" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
-      <c r="A2" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="2" spans="1:27">
+      <c r="A2" s="17" t="s">
         <v>27</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="3"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" s="5">
+        <v>1</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" s="5">
+        <f t="shared" ref="Y2:Y4" si="0">W2*X2</f>
+        <v>200000</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
+      <c r="A3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" s="5">
+        <v>2</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y3" s="5">
+        <f t="shared" si="0"/>
+        <v>200000</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" s="4">
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="3"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="W4" s="5">
+        <v>12</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" s="5">
+        <f t="shared" si="0"/>
+        <v>600000</v>
+      </c>
+      <c r="Z4" s="5">
         <v>1</v>
       </c>
-      <c r="U2" s="4">
-        <v>0</v>
-      </c>
-      <c r="V2" s="4">
-        <f t="shared" ref="V2:V3" si="0">S2*U2</f>
-        <v>0</v>
-      </c>
-      <c r="W2" s="4">
-        <v>0</v>
-      </c>
-      <c r="X2" s="5">
-        <v>1</v>
+      <c r="AA4" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3" s="4">
-        <v>2</v>
-      </c>
-      <c r="U3" s="4">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W3" s="4">
-        <v>0</v>
-      </c>
-      <c r="X3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
-      <c r="A4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" s="4">
-        <v>12</v>
-      </c>
-      <c r="U4" s="4">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:27">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="N4" r:id="rId3" display="xxx@gmail.com"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
@@ -1565,47 +1629,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/hddt-SES/src/main/resources/static/agent/MauUpload_PXK_HKGDL_TT78.xlsx
+++ b/hddt-SES/src/main/resources/static/agent/MauUpload_PXK_HKGDL_TT78.xlsx
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
   <si>
     <t>Mã phiếu(*)</t>
   </si>
@@ -83,7 +83,7 @@
     <t>Ngày lập (*)</t>
   </si>
   <si>
-    <t>Họ và tên người xuất kho (*)</t>
+    <t>Họ và tên người xuất kho</t>
   </si>
   <si>
     <t>Loại tiền (*)</t>
@@ -164,9 +164,6 @@
     <t>12/05/2026</t>
   </si>
   <si>
-    <t>Nguyễn Văn A</t>
-  </si>
-  <si>
     <t>VND</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>Xe</t>
   </si>
   <si>
-    <t>Tên đơn vị nhạp 1</t>
-  </si>
-  <si>
     <t>Địa chỉ kho nhập 1</t>
   </si>
   <si>
@@ -210,9 +204,6 @@
   </si>
   <si>
     <t>Tàu</t>
-  </si>
-  <si>
-    <t>Tên đơn vị nhạp 2</t>
   </si>
   <si>
     <t>Địa chỉ kho nhập 2</t>
@@ -1362,7 +1353,7 @@
       <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="9" t="s">
@@ -1445,54 +1436,42 @@
       <c r="C2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" s="3"/>
       <c r="O2" s="15"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
       <c r="S2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="T2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="W2" s="5">
         <v>1</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y2" s="5">
         <f t="shared" ref="Y2:Y4" si="0">W2*X2</f>
@@ -1510,22 +1489,22 @@
         <v>27</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="W3" s="5">
         <v>2</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Y3" s="5">
         <f t="shared" si="0"/>
@@ -1537,7 +1516,7 @@
     </row>
     <row r="4" spans="1:27">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>28</v>
@@ -1545,54 +1524,42 @@
       <c r="C4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" s="3"/>
+        <v>44</v>
+      </c>
       <c r="O4" s="16"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
         <v>27</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W4" s="5">
         <v>12</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Y4" s="5">
         <f t="shared" si="0"/>
@@ -1607,7 +1574,7 @@
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1629,47 +1596,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
